--- a/ams/cases/wecc/wecc_uced.xlsx
+++ b/ams/cases/wecc/wecc_uced.xlsx
@@ -17,9 +17,9 @@
     <sheet name="Line" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Zone" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="GCost" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="EDTSlot" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="EDSlot" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="EDSlotGen" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="UCTSlot" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="UCSlot" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="SFR" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="SFRCost" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="SR" sheetId="16" state="visible" r:id="rId16"/>

--- a/ams/cases/wecc/wecc_uced.xlsx
+++ b/ams/cases/wecc/wecc_uced.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Load factor in EDTSlot and UCTSlot sourced from CAISO forcasted hourly load on 2023 May 15</t>
+          <t>Load factor in EDSlotLoad and UCSlotLoad sourced from CAISO forcasted hourly load on 2023 May 15</t>
         </is>
       </c>
     </row>
